--- a/Errors_proper.xlsx
+++ b/Errors_proper.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cdepaor2\Desktop\EUCASS_2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E90C4E1-FC2F-42B8-8FC1-DB5209D90170}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ABB115C-3E40-4634-8A9A-8FFA492CFE00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" activeTab="1" xr2:uid="{26281CD5-8718-4C48-A2D9-78A497C5F058}"/>
   </bookViews>

--- a/Errors_proper.xlsx
+++ b/Errors_proper.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cdepaor2\Desktop\EUCASS_2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ABB115C-3E40-4634-8A9A-8FFA492CFE00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E38C3F4F-42D9-4F9F-A66C-26C9B8B77269}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" activeTab="1" xr2:uid="{26281CD5-8718-4C48-A2D9-78A497C5F058}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{26281CD5-8718-4C48-A2D9-78A497C5F058}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -528,20 +528,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B468F2C1-C6B4-4AF5-80F1-A4BF966E5AC0}">
   <dimension ref="A3:J14"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.33203125" customWidth="1"/>
-    <col min="3" max="3" width="22.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.21875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.21875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="21.21875" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="21" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.28515625" customWidth="1"/>
+    <col min="3" max="3" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="22.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="23.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="1" t="s">
         <v>0</v>
@@ -571,7 +572,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
@@ -603,7 +604,7 @@
         <v>10.425000000000001</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
@@ -635,7 +636,7 @@
         <v>36.244999999999997</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
@@ -667,7 +668,7 @@
         <v>61.11</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>11</v>
       </c>
@@ -699,7 +700,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>12</v>
       </c>
@@ -731,7 +732,7 @@
         <v>29.155000000000001</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>13</v>
       </c>
@@ -763,7 +764,7 @@
         <v>48.545000000000002</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>14</v>
       </c>
@@ -795,7 +796,7 @@
         <v>49.784999999999997</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>15</v>
       </c>
@@ -827,7 +828,7 @@
         <v>52.604999999999997</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>16</v>
       </c>
@@ -859,7 +860,7 @@
         <v>54.86</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>17</v>
       </c>
@@ -891,7 +892,7 @@
         <v>55.77</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
     </row>
   </sheetData>
@@ -902,13 +903,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DA1F874-8F33-43E1-894D-263665CCB481}">
   <dimension ref="A1:E24"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="18.77734375" customWidth="1"/>
-    <col min="3" max="3" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="3" width="15.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
         <v>20</v>
       </c>
@@ -916,7 +917,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
         <v>22</v>
       </c>
@@ -930,7 +931,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -945,7 +946,7 @@
         <v>1.9609999999999905E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -960,7 +961,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -975,7 +976,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -990,7 +991,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -1005,7 +1006,7 @@
         <v>1.5020000000000033E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>17</v>
       </c>
@@ -1020,7 +1021,7 @@
         <v>5.1299999999998569E-4</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>24</v>
       </c>
@@ -1028,7 +1029,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -1043,7 +1044,7 @@
         <v>1.9609999999999905E-3</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>13</v>
       </c>
@@ -1058,7 +1059,7 @@
         <v>1.5060000000000073E-3</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>14</v>
       </c>
@@ -1073,7 +1074,7 @@
         <v>2.6099999999995571E-4</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>15</v>
       </c>
@@ -1088,7 +1089,7 @@
         <v>4.6309999999999962E-3</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>16</v>
       </c>
@@ -1103,7 +1104,7 @@
         <v>1.5020000000000033E-3</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>17</v>
       </c>
@@ -1118,7 +1119,7 @@
         <v>5.1299999999998569E-4</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
         <v>27</v>
       </c>
@@ -1126,7 +1127,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>12</v>
       </c>
@@ -1141,7 +1142,7 @@
         <v>0.28167900000000001</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>13</v>
       </c>
@@ -1156,7 +1157,7 @@
         <v>0.15687899999999999</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>14</v>
       </c>
@@ -1171,7 +1172,7 @@
         <v>0.39012999999999998</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>15</v>
       </c>
@@ -1186,7 +1187,7 @@
         <v>0.66152499999999992</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>16</v>
       </c>
@@ -1201,7 +1202,7 @@
         <v>0.62814300000000001</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>17</v>
       </c>
@@ -1224,15 +1225,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A76EA2D4-9AC6-4894-BED9-178505A8CF51}">
   <dimension ref="B3:I13"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="21.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.88671875" customWidth="1"/>
-    <col min="5" max="5" width="23.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="20.44140625" customWidth="1"/>
+    <col min="3" max="3" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.85546875" customWidth="1"/>
+    <col min="5" max="5" width="23.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C3" s="1" t="s">
         <v>31</v>
       </c>
@@ -1252,7 +1253,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>8</v>
       </c>
@@ -1275,7 +1276,7 @@
         <v>-2.1800000000000002</v>
       </c>
     </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>9</v>
       </c>
@@ -1298,7 +1299,7 @@
         <v>-25.41</v>
       </c>
     </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>10</v>
       </c>
@@ -1321,7 +1322,7 @@
         <v>2.77</v>
       </c>
     </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>11</v>
       </c>
@@ -1344,7 +1345,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>12</v>
       </c>
@@ -1367,7 +1368,7 @@
         <v>-14.01</v>
       </c>
     </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>13</v>
       </c>
@@ -1390,7 +1391,7 @@
         <v>-30.56</v>
       </c>
     </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>14</v>
       </c>
@@ -1413,7 +1414,7 @@
         <v>499.23</v>
       </c>
     </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>15</v>
       </c>
@@ -1436,7 +1437,7 @@
         <v>-3.99</v>
       </c>
     </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>16</v>
       </c>
@@ -1459,7 +1460,7 @@
         <v>-16.28</v>
       </c>
     </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>17</v>
       </c>

--- a/Errors_proper.xlsx
+++ b/Errors_proper.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cdepaor2\Desktop\EUCASS_2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E38C3F4F-42D9-4F9F-A66C-26C9B8B77269}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FA33662-23C8-4F8F-A53F-2AFAA362D598}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{26281CD5-8718-4C48-A2D9-78A497C5F058}"/>
+    <workbookView xWindow="-44544" yWindow="1104" windowWidth="21600" windowHeight="11232" xr2:uid="{26281CD5-8718-4C48-A2D9-78A497C5F058}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
